--- a/tabular/reference/ervr/ervr_ltr_data_all.xlsx
+++ b/tabular/reference/ervr/ervr_ltr_data_all.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/erv_derived_elements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1433D307-8D4F-6D4F-8E54-6897C0D84EA3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB718DE-6DB9-4742-8077-E1701225D55D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="720" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="232">
   <si>
     <t>LTR_name</t>
   </si>
@@ -268,78 +268,6 @@
     <t>LTR35B</t>
   </si>
   <si>
-    <t>LTR19B</t>
-  </si>
-  <si>
-    <t>HUERS-P1</t>
-  </si>
-  <si>
-    <t>LTR19C</t>
-  </si>
-  <si>
-    <t>LTR73</t>
-  </si>
-  <si>
-    <t>LTR8</t>
-  </si>
-  <si>
-    <t>LTR8A</t>
-  </si>
-  <si>
-    <t>LTR8B</t>
-  </si>
-  <si>
-    <t>LTR1</t>
-  </si>
-  <si>
-    <t>HUERS-P2</t>
-  </si>
-  <si>
-    <t>LTR1A2</t>
-  </si>
-  <si>
-    <t>LTR1B</t>
-  </si>
-  <si>
-    <t>LTR1B0</t>
-  </si>
-  <si>
-    <t>LTR1B1</t>
-  </si>
-  <si>
-    <t>LTR1C</t>
-  </si>
-  <si>
-    <t>LTR1C1</t>
-  </si>
-  <si>
-    <t>LTR1D</t>
-  </si>
-  <si>
-    <t>LTR1D1</t>
-  </si>
-  <si>
-    <t>LTR1E</t>
-  </si>
-  <si>
-    <t>LTR1F</t>
-  </si>
-  <si>
-    <t>LTR1F1</t>
-  </si>
-  <si>
-    <t>LTR1F2</t>
-  </si>
-  <si>
-    <t>LTR28</t>
-  </si>
-  <si>
-    <t>LTR28B</t>
-  </si>
-  <si>
-    <t>LTR28C</t>
-  </si>
-  <si>
     <t>MER41A</t>
   </si>
   <si>
@@ -707,12 +635,6 @@
   </si>
   <si>
     <t>ERV-1.Zeta.35</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.W9P.P.1</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.W9P.P.2</t>
   </si>
   <si>
     <t>ERVR-1.Zeta.MER41</t>
@@ -1811,7 +1733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1831,16 +1753,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -1849,30 +1771,30 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>4</v>
@@ -1886,16 +1808,16 @@
         <v>31</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>6</v>
@@ -1912,16 +1834,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>6</v>
@@ -1938,16 +1860,16 @@
         <v>11</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>9</v>
@@ -1962,22 +1884,22 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>9</v>
@@ -1992,22 +1914,22 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>9</v>
@@ -2028,16 +1950,16 @@
         <v>12</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>9</v>
@@ -2058,16 +1980,16 @@
         <v>14</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>9</v>
@@ -2082,22 +2004,22 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>9</v>
@@ -2114,16 +2036,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>9</v>
@@ -2144,16 +2066,16 @@
         <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>9</v>
@@ -2174,16 +2096,16 @@
         <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>9</v>
@@ -2204,16 +2126,16 @@
         <v>21</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>19</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>9</v>
@@ -2234,16 +2156,16 @@
         <v>22</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>9</v>
@@ -2264,16 +2186,16 @@
         <v>24</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>9</v>
@@ -2294,16 +2216,16 @@
         <v>26</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>9</v>
@@ -2324,16 +2246,16 @@
         <v>27</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>9</v>
@@ -2354,16 +2276,16 @@
         <v>28</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>9</v>
@@ -2384,16 +2306,16 @@
         <v>30</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>9</v>
@@ -2414,16 +2336,16 @@
         <v>31</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>9</v>
@@ -2444,16 +2366,16 @@
         <v>32</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>29</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>9</v>
@@ -2474,16 +2396,16 @@
         <v>33</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>9</v>
@@ -2504,16 +2426,16 @@
         <v>35</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>9</v>
@@ -2534,16 +2456,16 @@
         <v>37</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>9</v>
@@ -2564,16 +2486,16 @@
         <v>38</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>9</v>
@@ -2594,16 +2516,16 @@
         <v>39</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>9</v>
@@ -2624,16 +2546,16 @@
         <v>40</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>9</v>
@@ -2654,16 +2576,16 @@
         <v>41</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>9</v>
@@ -2684,16 +2606,16 @@
         <v>42</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>9</v>
@@ -2714,16 +2636,16 @@
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>36</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>9</v>
@@ -2738,22 +2660,22 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>9</v>
@@ -2774,16 +2696,16 @@
         <v>44</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>9</v>
@@ -2804,16 +2726,16 @@
         <v>46</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>47</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>9</v>
@@ -2834,16 +2756,16 @@
         <v>48</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>9</v>
@@ -2864,16 +2786,16 @@
         <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>9</v>
@@ -2894,16 +2816,16 @@
         <v>51</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>9</v>
@@ -2924,16 +2846,16 @@
         <v>52</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>49</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>9</v>
@@ -2954,16 +2876,16 @@
         <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>54</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>9</v>
@@ -2984,16 +2906,16 @@
         <v>62</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>55</v>
@@ -3014,16 +2936,16 @@
         <v>63</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>55</v>
@@ -3044,16 +2966,16 @@
         <v>57</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>55</v>
@@ -3074,16 +2996,16 @@
         <v>59</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>55</v>
@@ -3092,7 +3014,7 @@
         <v>56</v>
       </c>
       <c r="I43" t="str">
-        <f t="shared" ref="I43:I74" si="1">IF(A43&lt;&gt;B43,"FLAG","")</f>
+        <f t="shared" ref="I43:I52" si="1">IF(A43&lt;&gt;B43,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3104,16 +3026,16 @@
         <v>60</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>55</v>
@@ -3134,16 +3056,16 @@
         <v>61</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>58</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>55</v>
@@ -3164,16 +3086,16 @@
         <v>66</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>67</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>55</v>
@@ -3194,16 +3116,16 @@
         <v>68</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>55</v>
@@ -3224,16 +3146,16 @@
         <v>70</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>69</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>55</v>
@@ -3254,16 +3176,16 @@
         <v>71</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>72</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>55</v>
@@ -3284,16 +3206,16 @@
         <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>72</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>55</v>
@@ -3314,16 +3236,16 @@
         <v>74</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>72</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>55</v>
@@ -3344,16 +3266,16 @@
         <v>75</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>72</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G52" s="5" t="s">
         <v>55</v>
@@ -3374,16 +3296,16 @@
         <v>76</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>72</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G53" s="5" t="s">
         <v>55</v>
@@ -3392,7 +3314,7 @@
         <v>4</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I53:I69" si="2">IF(A53&lt;&gt;B53,"FLAG","")</f>
         <v/>
       </c>
     </row>
@@ -3404,16 +3326,16 @@
         <v>77</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G54" s="5" t="s">
         <v>55</v>
@@ -3422,28 +3344,28 @@
         <v>4</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>79</v>
-      </c>
       <c r="F55" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>55</v>
@@ -3452,7 +3374,7 @@
         <v>4</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3464,16 +3386,16 @@
         <v>80</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G56" s="5" t="s">
         <v>55</v>
@@ -3482,7 +3404,7 @@
         <v>4</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3494,16 +3416,16 @@
         <v>81</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G57" s="5" t="s">
         <v>55</v>
@@ -3512,7 +3434,7 @@
         <v>4</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3524,16 +3446,16 @@
         <v>82</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>55</v>
@@ -3542,7 +3464,7 @@
         <v>4</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3554,16 +3476,16 @@
         <v>83</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>55</v>
@@ -3572,7 +3494,7 @@
         <v>4</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3584,16 +3506,16 @@
         <v>84</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G60" s="5" t="s">
         <v>55</v>
@@ -3602,7 +3524,7 @@
         <v>4</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3614,16 +3536,16 @@
         <v>85</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>55</v>
@@ -3632,7 +3554,7 @@
         <v>4</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3644,16 +3566,16 @@
         <v>86</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G62" s="5" t="s">
         <v>55</v>
@@ -3662,7 +3584,7 @@
         <v>4</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3674,16 +3596,16 @@
         <v>87</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>55</v>
@@ -3692,7 +3614,7 @@
         <v>4</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3704,16 +3626,16 @@
         <v>88</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>55</v>
@@ -3722,7 +3644,7 @@
         <v>4</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3734,16 +3656,16 @@
         <v>89</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>55</v>
@@ -3752,7 +3674,7 @@
         <v>4</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -3764,16 +3686,16 @@
         <v>90</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>55</v>
@@ -3782,28 +3704,28 @@
         <v>4</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>55</v>
@@ -3812,28 +3734,28 @@
         <v>4</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G68" s="5" t="s">
         <v>55</v>
@@ -3842,28 +3764,28 @@
         <v>4</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>55</v>
@@ -3872,28 +3794,28 @@
         <v>4</v>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G70" s="5" t="s">
         <v>55</v>
@@ -3901,29 +3823,25 @@
       <c r="H70" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I70" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G71" s="5" t="s">
         <v>55</v>
@@ -3931,29 +3849,25 @@
       <c r="H71" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I71" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>97</v>
+        <v>222</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>55</v>
@@ -3961,29 +3875,25 @@
       <c r="H72" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I72" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>55</v>
@@ -3991,29 +3901,25 @@
       <c r="H73" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I73" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>55</v>
@@ -4021,29 +3927,25 @@
       <c r="H74" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I74" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G75" s="5" t="s">
         <v>55</v>
@@ -4051,29 +3953,25 @@
       <c r="H75" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I75" t="str">
-        <f t="shared" ref="I75:I91" si="2">IF(A75&lt;&gt;B75,"FLAG","")</f>
-        <v/>
-      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G76" s="5" t="s">
         <v>55</v>
@@ -4081,398 +3979,394 @@
       <c r="H76" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I76" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="F77" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H77" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I77:I104" si="3">IF(A77&lt;&gt;B77,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I79" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="F80" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I80" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I81" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I82" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I83" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I85" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I87" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I88" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4484,25 +4378,25 @@
         <v>118</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I90" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4514,261 +4408,289 @@
         <v>119</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>120</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I91" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>239</v>
+        <v>123</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>239</v>
+        <v>124</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>237</v>
+        <v>203</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>238</v>
+        <v>171</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I92" t="str">
+        <f t="shared" si="3"/>
+        <v>FLAG</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I93" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>248</v>
+        <v>125</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>248</v>
+        <v>125</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I94" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>62</v>
+        <v>129</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I95" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I96" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I97" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>60</v>
+        <v>133</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I98" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I99" t="str">
-        <f t="shared" ref="I99:I126" si="3">IF(A99&lt;&gt;B99,"FLAG","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>4</v>
@@ -4780,25 +4702,25 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>4</v>
@@ -4810,25 +4732,25 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>4</v>
@@ -4840,25 +4762,25 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>4</v>
@@ -4870,25 +4792,25 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>4</v>
@@ -4900,778 +4822,174 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I105" t="str">
-        <f t="shared" si="3"/>
-        <v/>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I106" t="str">
-        <f t="shared" si="3"/>
-        <v/>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H107" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I107" t="str">
-        <f t="shared" si="3"/>
-        <v/>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>138</v>
+        <v>226</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="D108" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E108" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="E108" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="F108" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="I108" t="str">
-        <f t="shared" si="3"/>
-        <v/>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>4</v>
       </c>
       <c r="I109" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(A109&lt;&gt;B109,"FLAG","")</f>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I110" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A111" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E111" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H111" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I111" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A112" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I112" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A113" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D113" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H113" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I113" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A114" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D114" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="E114" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H114" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I114" t="str">
-        <f t="shared" si="3"/>
-        <v>FLAG</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A115" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D115" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E115" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H115" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I115" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A116" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E116" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H116" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I116" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A117" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D117" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E117" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G117" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H117" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I117" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A118" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D118" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H118" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I118" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A119" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H119" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I119" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A120" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H120" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I120" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A121" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D121" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G121" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H121" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I121" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A122" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D122" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="E122" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H122" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I122" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A123" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E123" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F123" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H123" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I123" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A124" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E124" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F124" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H124" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I124" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A125" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D125" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="E125" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H125" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I125" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A126" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="E126" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G126" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H126" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="I126" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A127" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D127" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E127" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="F127" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H127" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A128" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E128" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G128" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H128" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="F129" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G129" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H129" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="F130" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G130" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H130" s="5" t="s">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I129">
-    <sortCondition ref="C3:C129"/>
-    <sortCondition ref="G3:G129"/>
-    <sortCondition ref="H3:H129"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I107">
+    <sortCondition ref="C3:C107"/>
+    <sortCondition ref="G3:G107"/>
+    <sortCondition ref="H3:H107"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
-  <conditionalFormatting sqref="I114:I115">
+  <conditionalFormatting sqref="I92:I93">
     <cfRule type="containsText" dxfId="9" priority="13" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I114)))</formula>
+      <formula>NOT(ISERROR(SEARCH("FLAG",I92)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
@@ -5684,23 +5002,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I32:I113 I3:I4 I7:I30">
-    <cfRule type="containsText" dxfId="8" priority="43" operator="containsText" text="FLAG">
-      <formula>NOT(ISERROR(SEARCH("FLAG",I3)))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="44">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I5">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I5)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -5715,7 +5018,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I6">
-    <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I6)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -5730,7 +5033,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I31">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I31)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5745,10 +5048,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I32:I91 I3:I4 I7:I30">
+    <cfRule type="containsText" dxfId="0" priority="45" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I3)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5776,16 +5094,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -5794,18 +5112,18 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -5829,13 +5147,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C3" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -5859,13 +5177,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -5889,13 +5207,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="C5" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -5919,13 +5237,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="C6" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -5949,13 +5267,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -5979,13 +5297,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -6009,13 +5327,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="B9" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -6039,13 +5357,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="C10" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -6069,13 +5387,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -6099,13 +5417,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C12" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -6129,13 +5447,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -6159,13 +5477,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="C14" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -6189,13 +5507,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -6219,13 +5537,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C16" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -6245,13 +5563,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B17" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C17" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -6277,7 +5595,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
@@ -6301,13 +5619,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
@@ -6337,7 +5655,7 @@
         <v>64</v>
       </c>
       <c r="C20" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
@@ -6367,7 +5685,7 @@
         <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -6397,16 +5715,16 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F22" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -6421,25 +5739,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G23" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H23" t="s">
         <v>4</v>
@@ -6451,25 +5769,25 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H24" t="s">
         <v>4</v>
@@ -6481,25 +5799,25 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" t="s">
         <v>162</v>
       </c>
-      <c r="B25" t="s">
-        <v>162</v>
-      </c>
-      <c r="C25" t="s">
-        <v>186</v>
-      </c>
       <c r="D25" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G25" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H25" t="s">
         <v>4</v>
@@ -6511,25 +5829,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>4</v>
@@ -6541,25 +5859,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>4</v>
@@ -6571,7 +5889,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -6586,7 +5904,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -6601,7 +5919,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:I25">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -6616,7 +5934,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I26)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">

--- a/tabular/reference/ervr/ervr_ltr_data_all.xlsx
+++ b/tabular/reference/ervr/ervr_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8162BC7-CC24-604C-8463-C0387B774F03}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577523B6-E607-AF44-9E5B-0047A01DA989}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7740" yWindow="840" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="146">
   <si>
     <t>LTR_name</t>
   </si>
@@ -265,15 +265,6 @@
     <t>LTR40c</t>
   </si>
   <si>
-    <t>MER68</t>
-  </si>
-  <si>
-    <t>MER68B</t>
-  </si>
-  <si>
-    <t>MER68C</t>
-  </si>
-  <si>
     <t>MER74C</t>
   </si>
   <si>
@@ -379,9 +370,6 @@
     <t>HERV-L40</t>
   </si>
   <si>
-    <t>HERV-L68</t>
-  </si>
-  <si>
     <t>HERV-52</t>
   </si>
   <si>
@@ -472,9 +460,6 @@
     <t>ERVR-3.Lambda.52</t>
   </si>
   <si>
-    <t>ERVR-3.Lambda.68</t>
-  </si>
-  <si>
     <t>ERVR-3.Lambda.74</t>
   </si>
   <si>
@@ -488,6 +473,24 @@
   </si>
   <si>
     <t>HERV-57</t>
+  </si>
+  <si>
+    <t>MER110</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.110</t>
+  </si>
+  <si>
+    <t>ERVR-1.Theta.24.89</t>
+  </si>
+  <si>
+    <t>MER-89</t>
+  </si>
+  <si>
+    <t>MER89</t>
+  </si>
+  <si>
+    <t>MER-110</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1460,16 +1463,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -1480,22 +1483,22 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>16</v>
+        <v>144</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>143</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
@@ -1506,22 +1509,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
+        <v>140</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>140</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>9</v>
@@ -1532,22 +1535,22 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>121</v>
+        <v>16</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>9</v>
@@ -1557,75 +1560,75 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>20</v>
+      <c r="A5" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>135</v>
+        <v>110</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
+      <c r="A6" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>135</v>
+        <v>110</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>18</v>
@@ -1636,22 +1639,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>18</v>
@@ -1662,22 +1665,22 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>18</v>
@@ -1688,22 +1691,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>18</v>
@@ -1714,22 +1717,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>18</v>
@@ -1740,74 +1743,74 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>18</v>
@@ -1818,22 +1821,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>18</v>
@@ -1844,22 +1847,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>18</v>
@@ -1870,22 +1873,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>18</v>
@@ -1896,22 +1899,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>103</v>
+        <v>34</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>18</v>
@@ -1922,22 +1925,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>123</v>
+        <v>37</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>18</v>
@@ -1948,25 +1951,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>136</v>
+        <v>110</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>126</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>103</v>
+        <v>30</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>4</v>
@@ -1974,25 +1977,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>137</v>
+        <v>110</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>118</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>4</v>
@@ -2000,22 +2003,22 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>41</v>
@@ -2026,22 +2029,22 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G23" s="5" t="s">
         <v>41</v>
@@ -2052,22 +2055,22 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G24" s="5" t="s">
         <v>41</v>
@@ -2077,23 +2080,23 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>125</v>
+      <c r="A25" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>141</v>
+        <v>111</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>41</v>
@@ -2103,23 +2106,23 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>142</v>
+      <c r="A26" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>143</v>
+        <v>111</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>41</v>
@@ -2129,23 +2132,23 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>62</v>
+      <c r="A27" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>138</v>
+        <v>111</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>41</v>
@@ -2155,23 +2158,23 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>70</v>
+      <c r="A28" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>137</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D28" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>108</v>
-      </c>
       <c r="F28" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G28" s="5" t="s">
         <v>41</v>
@@ -2182,22 +2185,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>41</v>
@@ -2208,22 +2211,22 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>41</v>
@@ -2234,22 +2237,22 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>41</v>
@@ -2260,22 +2263,22 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>41</v>
@@ -2286,22 +2289,22 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>41</v>
@@ -2312,22 +2315,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G34" s="5" t="s">
         <v>41</v>
@@ -2338,22 +2341,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>41</v>
@@ -2364,22 +2367,22 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G36" s="5" t="s">
         <v>41</v>
@@ -2390,22 +2393,22 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G37" s="5" t="s">
         <v>41</v>
@@ -2416,22 +2419,22 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G38" s="5" t="s">
         <v>41</v>
@@ -2442,22 +2445,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>41</v>
@@ -2468,22 +2471,22 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>41</v>
@@ -2494,22 +2497,22 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>41</v>
@@ -2520,22 +2523,22 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>41</v>
@@ -2546,22 +2549,22 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>45</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>41</v>
@@ -2572,22 +2575,22 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>41</v>
@@ -2598,22 +2601,22 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G45" s="5" t="s">
         <v>41</v>
@@ -2624,22 +2627,22 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>41</v>
@@ -2650,22 +2653,22 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C47" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="E47" s="5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>41</v>
@@ -2674,38 +2677,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H48">
-    <sortCondition ref="C2:C48"/>
-    <sortCondition ref="G2:G48"/>
-    <sortCondition ref="H2:H48"/>
-    <sortCondition ref="D2:D48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H47">
+    <sortCondition ref="C4:C47"/>
+    <sortCondition ref="G4:G47"/>
+    <sortCondition ref="H4:H47"/>
+    <sortCondition ref="D4:D47"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2725,16 +2702,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>2</v>
@@ -2743,18 +2720,18 @@
         <v>3</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -2778,13 +2755,13 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -2808,13 +2785,13 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -2838,13 +2815,13 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -2868,13 +2845,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -2898,13 +2875,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -2928,13 +2905,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -2958,13 +2935,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -2988,13 +2965,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -3018,13 +2995,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -3048,13 +3025,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
         <v>95</v>
-      </c>
-      <c r="B12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -3078,13 +3055,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -3108,13 +3085,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -3144,7 +3121,7 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -3168,13 +3145,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -3194,13 +3171,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
         <v>95</v>
-      </c>
-      <c r="B17" t="s">
-        <v>95</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -3226,7 +3203,7 @@
         <v>5</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
@@ -3256,7 +3233,7 @@
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
@@ -3286,7 +3263,7 @@
         <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
@@ -3316,7 +3293,7 @@
         <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -3346,16 +3323,16 @@
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
         <v>8</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F22" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G22" t="s">
         <v>6</v>
@@ -3376,7 +3353,7 @@
         <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
         <v>41</v>
@@ -3385,7 +3362,7 @@
         <v>41</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
         <v>41</v>
@@ -3400,22 +3377,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E24" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
         <v>41</v>
@@ -3430,22 +3407,22 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E25" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
         <v>41</v>
@@ -3466,16 +3443,16 @@
         <v>40</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>41</v>
@@ -3496,16 +3473,16 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>42</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>41</v>

--- a/tabular/reference/ervr/ervr_ltr_data_all.xlsx
+++ b/tabular/reference/ervr/ervr_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577523B6-E607-AF44-9E5B-0047A01DA989}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56E78CF-97CD-6642-B180-B202E3CC12F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7740" yWindow="840" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tabular/reference/ervr/ervr_ltr_data_all.xlsx
+++ b/tabular/reference/ervr/ervr_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56E78CF-97CD-6642-B180-B202E3CC12F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABA26CA-1C40-DC4E-8188-D1B114563AAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7740" yWindow="840" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="157">
   <si>
     <t>LTR_name</t>
   </si>
@@ -491,6 +491,39 @@
   </si>
   <si>
     <t>MER-110</t>
+  </si>
+  <si>
+    <t>reference_role</t>
+  </si>
+  <si>
+    <t>reference_status</t>
+  </si>
+  <si>
+    <t>derivation_method</t>
+  </si>
+  <si>
+    <t>derivation_source</t>
+  </si>
+  <si>
+    <t>num_input_sequences</t>
+  </si>
+  <si>
+    <t>dfam_accession</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>canonical</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>consensus</t>
+  </si>
+  <si>
+    <t>repbase</t>
   </si>
 </sst>
 </file>
@@ -1092,7 +1125,17 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1443,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
@@ -1455,7 +1498,7 @@
     <col min="8" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1480,8 +1523,29 @@
       <c r="H1" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>144</v>
       </c>
@@ -1506,8 +1570,20 @@
       <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K2" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>140</v>
       </c>
@@ -1532,8 +1608,20 @@
       <c r="H3" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>16</v>
       </c>
@@ -1558,8 +1646,20 @@
       <c r="H4" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>153</v>
+      </c>
+      <c r="J4" t="s">
+        <v>154</v>
+      </c>
+      <c r="K4" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>10</v>
       </c>
@@ -1584,8 +1684,20 @@
       <c r="H5" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>153</v>
+      </c>
+      <c r="J5" t="s">
+        <v>154</v>
+      </c>
+      <c r="K5" t="s">
+        <v>155</v>
+      </c>
+      <c r="L5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>116</v>
       </c>
@@ -1610,8 +1722,20 @@
       <c r="H6" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1636,8 +1760,20 @@
       <c r="H7" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I7" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" t="s">
+        <v>154</v>
+      </c>
+      <c r="K7" t="s">
+        <v>155</v>
+      </c>
+      <c r="L7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
@@ -1662,8 +1798,20 @@
       <c r="H8" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J8" t="s">
+        <v>154</v>
+      </c>
+      <c r="K8" t="s">
+        <v>155</v>
+      </c>
+      <c r="L8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
@@ -1688,8 +1836,20 @@
       <c r="H9" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>153</v>
+      </c>
+      <c r="J9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K9" t="s">
+        <v>155</v>
+      </c>
+      <c r="L9" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
@@ -1714,8 +1874,20 @@
       <c r="H10" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>153</v>
+      </c>
+      <c r="J10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>123</v>
       </c>
@@ -1740,8 +1912,20 @@
       <c r="H11" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" t="s">
+        <v>155</v>
+      </c>
+      <c r="L11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1766,8 +1950,20 @@
       <c r="H12" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>153</v>
+      </c>
+      <c r="J12" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" t="s">
+        <v>155</v>
+      </c>
+      <c r="L12" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -1792,8 +1988,20 @@
       <c r="H13" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>153</v>
+      </c>
+      <c r="J13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" t="s">
+        <v>155</v>
+      </c>
+      <c r="L13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>14</v>
       </c>
@@ -1818,8 +2026,20 @@
       <c r="H14" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I14" t="s">
+        <v>153</v>
+      </c>
+      <c r="J14" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" t="s">
+        <v>155</v>
+      </c>
+      <c r="L14" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>15</v>
       </c>
@@ -1844,8 +2064,20 @@
       <c r="H15" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I15" t="s">
+        <v>153</v>
+      </c>
+      <c r="J15" t="s">
+        <v>154</v>
+      </c>
+      <c r="K15" t="s">
+        <v>155</v>
+      </c>
+      <c r="L15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -1870,8 +2102,20 @@
       <c r="H16" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I16" t="s">
+        <v>153</v>
+      </c>
+      <c r="J16" t="s">
+        <v>154</v>
+      </c>
+      <c r="K16" t="s">
+        <v>155</v>
+      </c>
+      <c r="L16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>33</v>
       </c>
@@ -1896,8 +2140,20 @@
       <c r="H17" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>153</v>
+      </c>
+      <c r="J17" t="s">
+        <v>154</v>
+      </c>
+      <c r="K17" t="s">
+        <v>155</v>
+      </c>
+      <c r="L17" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>35</v>
       </c>
@@ -1922,8 +2178,20 @@
       <c r="H18" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I18" t="s">
+        <v>153</v>
+      </c>
+      <c r="J18" t="s">
+        <v>154</v>
+      </c>
+      <c r="K18" t="s">
+        <v>155</v>
+      </c>
+      <c r="L18" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>36</v>
       </c>
@@ -1948,8 +2216,20 @@
       <c r="H19" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I19" t="s">
+        <v>153</v>
+      </c>
+      <c r="J19" t="s">
+        <v>154</v>
+      </c>
+      <c r="K19" t="s">
+        <v>155</v>
+      </c>
+      <c r="L19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
@@ -1974,8 +2254,20 @@
       <c r="H20" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I20" t="s">
+        <v>153</v>
+      </c>
+      <c r="J20" t="s">
+        <v>154</v>
+      </c>
+      <c r="K20" t="s">
+        <v>155</v>
+      </c>
+      <c r="L20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>120</v>
       </c>
@@ -2000,8 +2292,20 @@
       <c r="H21" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>153</v>
+      </c>
+      <c r="J21" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" t="s">
+        <v>155</v>
+      </c>
+      <c r="L21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>58</v>
       </c>
@@ -2026,8 +2330,20 @@
       <c r="H22" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I22" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" t="s">
+        <v>154</v>
+      </c>
+      <c r="K22" t="s">
+        <v>155</v>
+      </c>
+      <c r="L22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>64</v>
       </c>
@@ -2052,8 +2368,20 @@
       <c r="H23" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I23" t="s">
+        <v>153</v>
+      </c>
+      <c r="J23" t="s">
+        <v>154</v>
+      </c>
+      <c r="K23" t="s">
+        <v>155</v>
+      </c>
+      <c r="L23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>63</v>
       </c>
@@ -2078,8 +2406,20 @@
       <c r="H24" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I24" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" t="s">
+        <v>154</v>
+      </c>
+      <c r="K24" t="s">
+        <v>155</v>
+      </c>
+      <c r="L24" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>66</v>
       </c>
@@ -2104,8 +2444,20 @@
       <c r="H25" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I25" t="s">
+        <v>153</v>
+      </c>
+      <c r="J25" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>68</v>
       </c>
@@ -2130,8 +2482,20 @@
       <c r="H26" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I26" t="s">
+        <v>153</v>
+      </c>
+      <c r="J26" t="s">
+        <v>154</v>
+      </c>
+      <c r="K26" t="s">
+        <v>155</v>
+      </c>
+      <c r="L26" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>121</v>
       </c>
@@ -2156,8 +2520,20 @@
       <c r="H27" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I27" t="s">
+        <v>153</v>
+      </c>
+      <c r="J27" t="s">
+        <v>154</v>
+      </c>
+      <c r="K27" t="s">
+        <v>155</v>
+      </c>
+      <c r="L27" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>137</v>
       </c>
@@ -2182,8 +2558,20 @@
       <c r="H28" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I28" t="s">
+        <v>153</v>
+      </c>
+      <c r="J28" t="s">
+        <v>154</v>
+      </c>
+      <c r="K28" t="s">
+        <v>155</v>
+      </c>
+      <c r="L28" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>62</v>
       </c>
@@ -2208,8 +2596,20 @@
       <c r="H29" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I29" t="s">
+        <v>153</v>
+      </c>
+      <c r="J29" t="s">
+        <v>154</v>
+      </c>
+      <c r="K29" t="s">
+        <v>155</v>
+      </c>
+      <c r="L29" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>70</v>
       </c>
@@ -2234,8 +2634,20 @@
       <c r="H30" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I30" t="s">
+        <v>153</v>
+      </c>
+      <c r="J30" t="s">
+        <v>154</v>
+      </c>
+      <c r="K30" t="s">
+        <v>155</v>
+      </c>
+      <c r="L30" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>44</v>
       </c>
@@ -2260,8 +2672,20 @@
       <c r="H31" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I31" t="s">
+        <v>153</v>
+      </c>
+      <c r="J31" t="s">
+        <v>154</v>
+      </c>
+      <c r="K31" t="s">
+        <v>155</v>
+      </c>
+      <c r="L31" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>46</v>
       </c>
@@ -2286,8 +2710,20 @@
       <c r="H32" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I32" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" t="s">
+        <v>154</v>
+      </c>
+      <c r="K32" t="s">
+        <v>155</v>
+      </c>
+      <c r="L32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>47</v>
       </c>
@@ -2312,8 +2748,20 @@
       <c r="H33" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I33" t="s">
+        <v>153</v>
+      </c>
+      <c r="J33" t="s">
+        <v>154</v>
+      </c>
+      <c r="K33" t="s">
+        <v>155</v>
+      </c>
+      <c r="L33" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>48</v>
       </c>
@@ -2338,8 +2786,20 @@
       <c r="H34" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I34" t="s">
+        <v>153</v>
+      </c>
+      <c r="J34" t="s">
+        <v>154</v>
+      </c>
+      <c r="K34" t="s">
+        <v>155</v>
+      </c>
+      <c r="L34" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>49</v>
       </c>
@@ -2364,8 +2824,20 @@
       <c r="H35" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I35" t="s">
+        <v>153</v>
+      </c>
+      <c r="J35" t="s">
+        <v>154</v>
+      </c>
+      <c r="K35" t="s">
+        <v>155</v>
+      </c>
+      <c r="L35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>50</v>
       </c>
@@ -2390,8 +2862,20 @@
       <c r="H36" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I36" t="s">
+        <v>153</v>
+      </c>
+      <c r="J36" t="s">
+        <v>154</v>
+      </c>
+      <c r="K36" t="s">
+        <v>155</v>
+      </c>
+      <c r="L36" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>51</v>
       </c>
@@ -2416,8 +2900,20 @@
       <c r="H37" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I37" t="s">
+        <v>153</v>
+      </c>
+      <c r="J37" t="s">
+        <v>154</v>
+      </c>
+      <c r="K37" t="s">
+        <v>155</v>
+      </c>
+      <c r="L37" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>52</v>
       </c>
@@ -2442,8 +2938,20 @@
       <c r="H38" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I38" t="s">
+        <v>153</v>
+      </c>
+      <c r="J38" t="s">
+        <v>154</v>
+      </c>
+      <c r="K38" t="s">
+        <v>155</v>
+      </c>
+      <c r="L38" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>53</v>
       </c>
@@ -2468,8 +2976,20 @@
       <c r="H39" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I39" t="s">
+        <v>153</v>
+      </c>
+      <c r="J39" t="s">
+        <v>154</v>
+      </c>
+      <c r="K39" t="s">
+        <v>155</v>
+      </c>
+      <c r="L39" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>54</v>
       </c>
@@ -2494,8 +3014,20 @@
       <c r="H40" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I40" t="s">
+        <v>153</v>
+      </c>
+      <c r="J40" t="s">
+        <v>154</v>
+      </c>
+      <c r="K40" t="s">
+        <v>155</v>
+      </c>
+      <c r="L40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>55</v>
       </c>
@@ -2520,8 +3052,20 @@
       <c r="H41" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I41" t="s">
+        <v>153</v>
+      </c>
+      <c r="J41" t="s">
+        <v>154</v>
+      </c>
+      <c r="K41" t="s">
+        <v>155</v>
+      </c>
+      <c r="L41" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>56</v>
       </c>
@@ -2546,8 +3090,20 @@
       <c r="H42" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I42" t="s">
+        <v>153</v>
+      </c>
+      <c r="J42" t="s">
+        <v>154</v>
+      </c>
+      <c r="K42" t="s">
+        <v>155</v>
+      </c>
+      <c r="L42" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>57</v>
       </c>
@@ -2572,8 +3128,20 @@
       <c r="H43" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I43" t="s">
+        <v>153</v>
+      </c>
+      <c r="J43" t="s">
+        <v>154</v>
+      </c>
+      <c r="K43" t="s">
+        <v>155</v>
+      </c>
+      <c r="L43" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>74</v>
       </c>
@@ -2598,8 +3166,20 @@
       <c r="H44" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I44" t="s">
+        <v>153</v>
+      </c>
+      <c r="J44" t="s">
+        <v>154</v>
+      </c>
+      <c r="K44" t="s">
+        <v>155</v>
+      </c>
+      <c r="L44" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>76</v>
       </c>
@@ -2624,8 +3204,20 @@
       <c r="H45" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I45" t="s">
+        <v>153</v>
+      </c>
+      <c r="J45" t="s">
+        <v>154</v>
+      </c>
+      <c r="K45" t="s">
+        <v>155</v>
+      </c>
+      <c r="L45" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>77</v>
       </c>
@@ -2650,8 +3242,20 @@
       <c r="H46" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I46" t="s">
+        <v>153</v>
+      </c>
+      <c r="J46" t="s">
+        <v>154</v>
+      </c>
+      <c r="K46" t="s">
+        <v>155</v>
+      </c>
+      <c r="L46" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>78</v>
       </c>
@@ -2675,6 +3279,18 @@
       </c>
       <c r="H47" s="5" t="s">
         <v>4</v>
+      </c>
+      <c r="I47" t="s">
+        <v>153</v>
+      </c>
+      <c r="J47" t="s">
+        <v>154</v>
+      </c>
+      <c r="K47" t="s">
+        <v>155</v>
+      </c>
+      <c r="L47" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2685,6 +3301,21 @@
     <sortCondition ref="D4:D47"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
+  <conditionalFormatting sqref="I2:I47">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+      <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3497,7 +4128,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -3512,7 +4143,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -3527,7 +4158,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:I25">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3542,7 +4173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I26)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">

--- a/tabular/reference/ervr/ervr_ltr_data_all.xlsx
+++ b/tabular/reference/ervr/ervr_ltr_data_all.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/ervr/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABA26CA-1C40-DC4E-8188-D1B114563AAB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CB93DF-C9FC-F947-B66C-DEB333595E31}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7740" yWindow="840" windowWidth="21060" windowHeight="16940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3302,7 +3302,7 @@
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="I2:I47">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -4128,7 +4128,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I22">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I2)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
@@ -4143,7 +4143,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I23">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I23)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -4158,7 +4158,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I24:I25">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I24)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4173,7 +4173,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I26:I27">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="FLAG">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="FLAG">
       <formula>NOT(ISERROR(SEARCH("FLAG",I26)))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
